--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -214,7 +214,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -225,6 +229,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:G12" totalsRowShown="0">
+  <autoFilter ref="A1:G12"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Sr. No."/>
+    <tableColumn id="2" name="Project / Issue"/>
+    <tableColumn id="3" name="UAT/Live"/>
+    <tableColumn id="4" name="Current NBP Remarks"/>
+    <tableColumn id="5" name="PAYSYS Response"/>
+    <tableColumn id="6" name="NBP Remarks / Action Required"/>
+    <tableColumn id="7" name="Last Update Date" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,7 +539,7 @@
     <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="130.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -748,7 +768,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>36</v>
@@ -762,6 +782,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -161,6 +161,18 @@
   </si>
   <si>
     <t xml:space="preserve">Waiting </t>
+  </si>
+  <si>
+    <t>RAAST P2P &amp; Bulk Raast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAAST P2P &amp; Bulk Raast Environment UP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">96 Hours Timeline </t>
+  </si>
+  <si>
+    <t>set 48 hours to 96 hours time period for end to end transactions</t>
   </si>
 </sst>
 </file>
@@ -201,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -210,13 +222,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -232,11 +250,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:G12" totalsRowShown="0">
-  <autoFilter ref="A1:G12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:G14" totalsRowShown="0">
+  <autoFilter ref="A1:G14"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sr. No."/>
-    <tableColumn id="2" name="Project / Issue"/>
+    <tableColumn id="2" name="Project / Issue" dataDxfId="1"/>
     <tableColumn id="3" name="UAT/Live"/>
     <tableColumn id="4" name="Current NBP Remarks"/>
     <tableColumn id="5" name="PAYSYS Response"/>
@@ -532,10 +550,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="130.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
@@ -547,7 +565,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -570,7 +588,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -590,7 +608,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
@@ -610,7 +628,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
@@ -630,7 +648,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
@@ -650,7 +668,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
@@ -670,17 +688,14 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
+      <c r="B7" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
+      <c r="D7" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="G7" s="3">
         <v>46269</v>
@@ -690,17 +705,17 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G8" s="3">
         <v>46269</v>
@@ -710,8 +725,8 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>31</v>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -730,17 +745,17 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>32</v>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G10" s="3">
         <v>46269</v>
@@ -750,17 +765,14 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
+      <c r="B11" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G11" s="3">
         <v>46269</v>
@@ -770,14 +782,57 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>38</v>
+      </c>
+      <c r="G14" s="3">
+        <v>46269</v>
       </c>
     </row>
   </sheetData>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -52,9 +52,6 @@
     <t>SOW awaiting – API required for status update</t>
   </si>
   <si>
-    <t>Efforts awaited till Monday</t>
-  </si>
-  <si>
     <t>SWAPS</t>
   </si>
   <si>
@@ -64,18 +61,6 @@
     <t>SIT in progress since long – Overdue timeline</t>
   </si>
   <si>
-    <t>Project is delayed</t>
-  </si>
-  <si>
-    <t>QR Upload</t>
-  </si>
-  <si>
-    <t>Discussion required</t>
-  </si>
-  <si>
-    <t>To be discuss with CRPL</t>
-  </si>
-  <si>
     <t>RAAST OTC Reversal</t>
   </si>
   <si>
@@ -85,60 +70,36 @@
     <t>No update – Pending since long</t>
   </si>
   <si>
-    <t>Paysys to check and confirm</t>
-  </si>
-  <si>
     <t>Bulk Upload 50K – UAT Queries</t>
   </si>
   <si>
     <t>Queries shared with Haris – No response on queries raised</t>
   </si>
   <si>
-    <t>To be explore by Paysys by Wednesday</t>
-  </si>
-  <si>
     <t>OTC Biller – NTC</t>
   </si>
   <si>
     <t>UNDER UAT</t>
   </si>
   <si>
-    <t>Still unresolved API issue</t>
-  </si>
-  <si>
     <t>OTC Biller – UOBS</t>
   </si>
   <si>
     <t>No Update</t>
   </si>
   <si>
-    <t>to be check by paysys team</t>
-  </si>
-  <si>
     <t>OTC Biller – Pak Austria</t>
   </si>
   <si>
     <t xml:space="preserve">Resend UBCS Cut off Time </t>
   </si>
   <si>
-    <t>12:00 am to be cut-off as per previous pratice</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hourly UBCS Report </t>
   </si>
   <si>
     <t xml:space="preserve">NBP Receving only summary in UBCS Hourly rejected report. Transactions details addition required in the report. Report attach for your review </t>
   </si>
   <si>
-    <t>Follow Up Meeting Date/Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next Meeting </t>
-  </si>
-  <si>
-    <t>Wednesday 9/9/2026 1:00 PM</t>
-  </si>
-  <si>
     <t>Meeting</t>
   </si>
   <si>
@@ -160,9 +121,6 @@
     <t xml:space="preserve">Response shared to paysys </t>
   </si>
   <si>
-    <t xml:space="preserve">Waiting </t>
-  </si>
-  <si>
     <t>RAAST P2P &amp; Bulk Raast</t>
   </si>
   <si>
@@ -173,6 +131,72 @@
   </si>
   <si>
     <t>set 48 hours to 96 hours time period for end to end transactions</t>
+  </si>
+  <si>
+    <t>Will be confirm from Sami Khan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please share on priority </t>
+  </si>
+  <si>
+    <t>Cases will be share by NBP team</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAT Required </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK Up the UAT Envorniment </t>
+  </si>
+  <si>
+    <t>Will share update on Thursday</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will be available tommorow </t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>will be go Live</t>
+  </si>
+  <si>
+    <t>Please share date when it go live</t>
+  </si>
+  <si>
+    <t>Yaher will confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response awaited </t>
+  </si>
+  <si>
+    <t>Approval Required from NBP</t>
+  </si>
+  <si>
+    <t>Please share Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sami Afreen will confirm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kindly confirm via a email </t>
+  </si>
+  <si>
+    <t>Sami Afreen will update the report tommorow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBCS NADRA Isuue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Link and NADRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take Up with Mashood </t>
   </si>
 </sst>
 </file>
@@ -193,12 +217,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -213,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -225,13 +255,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -250,15 +297,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:G14" totalsRowShown="0">
-  <autoFilter ref="A1:G14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G13" totalsRowShown="0">
+  <autoFilter ref="A1:G13"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sr. No."/>
-    <tableColumn id="2" name="Project / Issue" dataDxfId="1"/>
+    <tableColumn id="2" name="Project / Issue" dataDxfId="3"/>
     <tableColumn id="3" name="UAT/Live"/>
     <tableColumn id="4" name="Current NBP Remarks"/>
-    <tableColumn id="5" name="PAYSYS Response"/>
-    <tableColumn id="6" name="NBP Remarks / Action Required"/>
+    <tableColumn id="5" name="PAYSYS Response" dataDxfId="2"/>
+    <tableColumn id="6" name="NBP Remarks / Action Required" dataDxfId="1"/>
     <tableColumn id="7" name="Last Update Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -597,11 +644,14 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
+      <c r="E2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="G2" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -609,19 +659,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="G3" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -629,19 +682,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
+      <c r="E4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="G4" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -649,19 +705,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="G5" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -669,19 +728,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
+      <c r="D6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="G6" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -689,16 +751,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G7" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -706,19 +774,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="G8" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -726,19 +797,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="G9" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -746,19 +820,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="G10" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -766,16 +843,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>32</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="G11" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -783,19 +866,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="G12" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -803,37 +889,27 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G13" s="3">
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="3">
-        <v>46269</v>
-      </c>
+      <c r="B14"/>
+      <c r="G14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -854,26 +930,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t xml:space="preserve">Take Up with Mashood </t>
+  </si>
+  <si>
+    <t>UBCS IS evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evidence Required </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email followup shared </t>
   </si>
 </sst>
 </file>
@@ -297,8 +309,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G13" totalsRowShown="0">
-  <autoFilter ref="A1:G13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G14" totalsRowShown="0">
+  <autoFilter ref="A1:G14"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sr. No."/>
     <tableColumn id="2" name="Project / Issue" dataDxfId="3"/>
@@ -597,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -908,8 +920,31 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14"/>
-      <c r="G14"/>
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="3">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15"/>
+      <c r="G15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -76,12 +76,6 @@
     <t>Queries shared with Haris – No response on queries raised</t>
   </si>
   <si>
-    <t>OTC Biller – NTC</t>
-  </si>
-  <si>
-    <t>UNDER UAT</t>
-  </si>
-  <si>
     <t>OTC Biller – UOBS</t>
   </si>
   <si>
@@ -91,15 +85,6 @@
     <t>OTC Biller – Pak Austria</t>
   </si>
   <si>
-    <t xml:space="preserve">Resend UBCS Cut off Time </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hourly UBCS Report </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBP Receving only summary in UBCS Hourly rejected report. Transactions details addition required in the report. Report attach for your review </t>
-  </si>
-  <si>
     <t>Meeting</t>
   </si>
   <si>
@@ -118,21 +103,12 @@
     <t>Track project status, PAYSYS response, NBP remarks/action items, and latest update date.</t>
   </si>
   <si>
-    <t xml:space="preserve">Response shared to paysys </t>
-  </si>
-  <si>
     <t>RAAST P2P &amp; Bulk Raast</t>
   </si>
   <si>
     <t xml:space="preserve">RAAST P2P &amp; Bulk Raast Environment UP </t>
   </si>
   <si>
-    <t xml:space="preserve">96 Hours Timeline </t>
-  </si>
-  <si>
-    <t>set 48 hours to 96 hours time period for end to end transactions</t>
-  </si>
-  <si>
     <t>Will be confirm from Sami Khan</t>
   </si>
   <si>
@@ -163,52 +139,16 @@
     <t>Ok</t>
   </si>
   <si>
-    <t>will be go Live</t>
-  </si>
-  <si>
-    <t>Please share date when it go live</t>
-  </si>
-  <si>
     <t>Yaher will confirm</t>
   </si>
   <si>
     <t xml:space="preserve">Response awaited </t>
   </si>
   <si>
-    <t>Approval Required from NBP</t>
-  </si>
-  <si>
-    <t>Please share Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sami Afreen will confirm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kindly confirm via a email </t>
-  </si>
-  <si>
-    <t>Sami Afreen will update the report tommorow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBCS NADRA Isuue </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Link and NADRA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Take Up with Mashood </t>
-  </si>
-  <si>
-    <t>UBCS IS evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence Required </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email followup shared </t>
+    <t>No update</t>
+  </si>
+  <si>
+    <t>Collection via Mobile app</t>
   </si>
 </sst>
 </file>
@@ -309,8 +249,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G14" totalsRowShown="0">
-  <autoFilter ref="A1:G14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G9" totalsRowShown="0">
+  <autoFilter ref="A1:G9"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sr. No."/>
     <tableColumn id="2" name="Project / Issue" dataDxfId="3"/>
@@ -609,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -657,10 +597,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3">
         <v>46280</v>
@@ -680,10 +620,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G3" s="3">
         <v>46280</v>
@@ -703,10 +643,10 @@
         <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G4" s="3">
         <v>46280</v>
@@ -726,10 +666,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G5" s="3">
         <v>46280</v>
@@ -740,42 +680,35 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="3">
-        <v>46280</v>
-      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
-        <v>19</v>
+      <c r="D7" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G7" s="3">
         <v>46280</v>
@@ -786,19 +719,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3">
         <v>46280</v>
@@ -809,142 +742,27 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3">
         <v>46280</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="3">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="3">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="3">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="3">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="3">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15"/>
-      <c r="G15"/>
+      <c r="B10"/>
+      <c r="G10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -965,26 +783,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Bulk Upload 50K – UAT Queries</t>
   </si>
   <si>
-    <t>Queries shared with Haris – No response on queries raised</t>
-  </si>
-  <si>
     <t>OTC Biller – UOBS</t>
   </si>
   <si>
@@ -145,10 +142,22 @@
     <t xml:space="preserve">Response awaited </t>
   </si>
   <si>
-    <t>No update</t>
-  </si>
-  <si>
     <t>Collection via Mobile app</t>
+  </si>
+  <si>
+    <t>Raast Limit 10K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting with paysys 11 AM to 12 PM </t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Advance Payment/ Control Gap</t>
+  </si>
+  <si>
+    <t>Link Shared</t>
   </si>
 </sst>
 </file>
@@ -249,8 +258,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G9" totalsRowShown="0">
-  <autoFilter ref="A1:G9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G10" totalsRowShown="0">
+  <autoFilter ref="A1:G10"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sr. No."/>
     <tableColumn id="2" name="Project / Issue" dataDxfId="3"/>
@@ -597,10 +606,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="G2" s="3">
         <v>46280</v>
@@ -620,10 +629,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="G3" s="3">
         <v>46280</v>
@@ -643,10 +652,10 @@
         <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="G4" s="3">
         <v>46280</v>
@@ -663,13 +672,13 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="G5" s="3">
         <v>46280</v>
@@ -680,13 +689,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -696,19 +705,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="G7" s="3">
         <v>46280</v>
@@ -719,19 +728,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="G8" s="3">
         <v>46280</v>
@@ -742,27 +751,44 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="G9" s="3">
         <v>46280</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10"/>
-      <c r="G10"/>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3">
+        <v>46300</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -783,26 +809,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -49,18 +49,12 @@
     <t>UAT</t>
   </si>
   <si>
-    <t>SOW awaiting – API required for status update</t>
-  </si>
-  <si>
     <t>SWAPS</t>
   </si>
   <si>
     <t xml:space="preserve">UAT </t>
   </si>
   <si>
-    <t>SIT in progress since long – Overdue timeline</t>
-  </si>
-  <si>
     <t>RAAST OTC Reversal</t>
   </si>
   <si>
@@ -70,15 +64,9 @@
     <t>No update – Pending since long</t>
   </si>
   <si>
-    <t>Bulk Upload 50K – UAT Queries</t>
-  </si>
-  <si>
     <t>OTC Biller – UOBS</t>
   </si>
   <si>
-    <t>No Update</t>
-  </si>
-  <si>
     <t>OTC Biller – Pak Austria</t>
   </si>
   <si>
@@ -100,64 +88,58 @@
     <t>Track project status, PAYSYS response, NBP remarks/action items, and latest update date.</t>
   </si>
   <si>
-    <t>RAAST P2P &amp; Bulk Raast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAAST P2P &amp; Bulk Raast Environment UP </t>
-  </si>
-  <si>
-    <t>Will be confirm from Sami Khan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please share on priority </t>
-  </si>
-  <si>
-    <t>Cases will be share by NBP team</t>
-  </si>
-  <si>
-    <t>WIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAT Required </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK Up the UAT Envorniment </t>
-  </si>
-  <si>
-    <t>Will share update on Thursday</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will be available tommorow </t>
-  </si>
-  <si>
-    <t>Ok</t>
-  </si>
-  <si>
-    <t>Yaher will confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Response awaited </t>
-  </si>
-  <si>
     <t>Collection via Mobile app</t>
   </si>
   <si>
-    <t>Raast Limit 10K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting with paysys 11 AM to 12 PM </t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Advance Payment/ Control Gap</t>
   </si>
   <si>
-    <t>Link Shared</t>
+    <t>SIT Complete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re Attempt </t>
+  </si>
+  <si>
+    <t>Email shared by NBP. Response Awaited from Paysys.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API Billers Data </t>
+  </si>
+  <si>
+    <t>Resonse awaited.</t>
+  </si>
+  <si>
+    <t>OTC Biller – PHC</t>
+  </si>
+  <si>
+    <t>UBPS Issue</t>
+  </si>
+  <si>
+    <t>Success response shared to channel but transactions failed at 1 Link end.</t>
+  </si>
+  <si>
+    <t>RAAST Bulk Issue</t>
+  </si>
+  <si>
+    <t>Update required</t>
+  </si>
+  <si>
+    <t>New Biller</t>
+  </si>
+  <si>
+    <t>UAT Complete</t>
+  </si>
+  <si>
+    <t>UAT awaited</t>
+  </si>
+  <si>
+    <t>Unable to connect please try again.</t>
+  </si>
+  <si>
+    <t>Slot for UAT if Required.</t>
+  </si>
+  <si>
+    <t>Lastest Update? CR approved by NBP.</t>
   </si>
 </sst>
 </file>
@@ -258,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G10" totalsRowShown="0">
-  <autoFilter ref="A1:G10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G13" totalsRowShown="0">
+  <autoFilter ref="A1:G13"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sr. No."/>
     <tableColumn id="2" name="Project / Issue" dataDxfId="3"/>
@@ -558,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -603,14 +585,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>29</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="3">
         <v>46280</v>
       </c>
@@ -620,20 +598,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
       <c r="G3" s="3">
         <v>46280</v>
       </c>
@@ -643,20 +617,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="3">
         <v>46280</v>
       </c>
@@ -666,20 +636,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>35</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="3">
         <v>46280</v>
       </c>
@@ -689,13 +655,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -705,20 +671,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>37</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="3">
         <v>46280</v>
       </c>
@@ -728,20 +690,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
       <c r="G8" s="3">
         <v>46280</v>
       </c>
@@ -751,43 +709,83 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="3">
         <v>46280</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="B12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="3">
         <v>46300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -809,26 +807,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -140,6 +140,18 @@
   </si>
   <si>
     <t>Lastest Update? CR approved by NBP.</t>
+  </si>
+  <si>
+    <t>RAAST P2P</t>
+  </si>
+  <si>
+    <t>Single RAAST Transaction via Smartpay</t>
+  </si>
+  <si>
+    <t>RAAST via RF Account</t>
+  </si>
+  <si>
+    <t>Debit Hold Failed at PAYSYS End</t>
   </si>
 </sst>
 </file>
@@ -240,8 +252,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G13" totalsRowShown="0">
-  <autoFilter ref="A1:G13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:G15" totalsRowShown="0">
+  <autoFilter ref="A1:G15"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sr. No."/>
     <tableColumn id="2" name="Project / Issue" dataDxfId="3"/>
@@ -540,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -617,67 +629,64 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="3">
-        <v>46280</v>
-      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="3">
-        <v>46280</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
+      <c r="G6" s="3">
+        <v>46280</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -687,35 +696,32 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="3">
-        <v>46280</v>
-      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -725,66 +731,104 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
+      <c r="G10" s="3">
+        <v>46280</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
+      <c r="G11" s="3">
+        <v>46280</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="3">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>38</v>
       </c>
     </row>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -115,9 +115,6 @@
     <t>UBPS Issue</t>
   </si>
   <si>
-    <t>Success response shared to channel but transactions failed at 1 Link end.</t>
-  </si>
-  <si>
     <t>RAAST Bulk Issue</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>UAT awaited</t>
   </si>
   <si>
-    <t>Unable to connect please try again.</t>
-  </si>
-  <si>
     <t>Slot for UAT if Required.</t>
   </si>
   <si>
@@ -152,6 +146,12 @@
   </si>
   <si>
     <t>Debit Hold Failed at PAYSYS End</t>
+  </si>
+  <si>
+    <t>Session with PAYSYS on RAAST</t>
+  </si>
+  <si>
+    <t>Success response shared to channel but transactions failed at 1 Link end. Report Required of rejected trasnactions.</t>
   </si>
 </sst>
 </file>
@@ -597,7 +597,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -629,13 +629,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -645,13 +645,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -705,7 +705,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -740,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -759,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -778,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -794,7 +794,7 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -804,13 +804,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
+++ b/data/PAYSYS_Weekly_Project_Update_04-Sep-2026.xlsx
@@ -91,9 +91,6 @@
     <t>Collection via Mobile app</t>
   </si>
   <si>
-    <t>Advance Payment/ Control Gap</t>
-  </si>
-  <si>
     <t>SIT Complete.</t>
   </si>
   <si>
@@ -130,9 +127,6 @@
     <t>UAT awaited</t>
   </si>
   <si>
-    <t>Slot for UAT if Required.</t>
-  </si>
-  <si>
     <t>Lastest Update? CR approved by NBP.</t>
   </si>
   <si>
@@ -152,6 +146,12 @@
   </si>
   <si>
     <t>Success response shared to channel but transactions failed at 1 Link end. Report Required of rejected trasnactions.</t>
+  </si>
+  <si>
+    <t>Failed Transactions Alert</t>
+  </si>
+  <si>
+    <t>We required email alert for RAAST, UBPS, IBFT and Raast OTC transactions.</t>
   </si>
 </sst>
 </file>
@@ -597,12 +597,12 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="3">
-        <v>46280</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -616,12 +616,12 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="3">
-        <v>46280</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -629,32 +629,38 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
+      <c r="G4" s="3">
+        <v>46310</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
+      <c r="G5" s="3">
+        <v>46310</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -672,7 +678,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
-        <v>46280</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -680,18 +686,18 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="3">
-        <v>46280</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -705,28 +711,31 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
+      <c r="G8" s="3">
+        <v>46310</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
-        <v>46280</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -740,12 +749,12 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
-        <v>46280</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -759,12 +768,12 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="3">
-        <v>46280</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,64 +781,75 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
+      <c r="G12" s="3">
+        <v>46310</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
+      <c r="G13" s="3">
+        <v>46310</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
-        <v>46300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>43</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="3">
+        <v>46310</v>
       </c>
     </row>
   </sheetData>
